--- a/cellstocks/exports/grid-roster.xlsx
+++ b/cellstocks/exports/grid-roster.xlsx
@@ -154,6 +154,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -216,6 +221,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -278,6 +288,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -340,6 +355,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -402,6 +422,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -464,6 +489,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -526,6 +556,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -588,6 +623,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -650,6 +690,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -712,6 +757,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -774,6 +824,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -836,6 +891,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -898,6 +958,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -960,6 +1025,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1022,6 +1092,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1084,6 +1159,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1146,6 +1226,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1208,6 +1293,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1270,6 +1360,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1332,6 +1427,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1394,6 +1494,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1456,6 +1561,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1518,6 +1628,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1575,6 +1690,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1632,6 +1752,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1689,6 +1814,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2411,6 +2541,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2473,6 +2608,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2535,6 +2675,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2597,6 +2742,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2659,6 +2809,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2721,6 +2876,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2778,6 +2938,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2835,6 +3000,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2892,6 +3062,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2954,6 +3129,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3016,6 +3196,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3078,6 +3263,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3140,6 +3330,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3202,6 +3397,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3264,6 +3464,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3326,6 +3531,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3388,6 +3598,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3445,6 +3660,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3502,6 +3722,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3564,6 +3789,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3626,6 +3856,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3688,6 +3923,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3750,6 +3990,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3812,6 +4057,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3869,6 +4119,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3926,6 +4181,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3983,6 +4243,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4040,6 +4305,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4097,6 +4367,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4159,6 +4434,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -4221,6 +4501,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -4283,6 +4568,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -4345,6 +4635,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -4407,6 +4702,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4469,6 +4769,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4526,6 +4831,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4583,6 +4893,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4640,6 +4955,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4697,6 +5017,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4754,6 +5079,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4816,6 +5146,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4878,6 +5213,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4935,6 +5275,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -4992,6 +5337,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -5049,6 +5399,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5106,6 +5461,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5163,6 +5523,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5220,6 +5585,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5282,6 +5652,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5344,6 +5719,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5406,6 +5786,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5468,6 +5853,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5530,6 +5920,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5592,6 +5987,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5978,6 +6378,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6040,6 +6445,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6097,6 +6507,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -6159,6 +6574,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6221,6 +6641,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6283,6 +6708,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -6345,6 +6775,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6407,6 +6842,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6469,6 +6909,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6531,6 +6976,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6593,6 +7043,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6655,6 +7110,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6717,6 +7177,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6779,6 +7244,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6841,6 +7311,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6903,6 +7378,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6965,6 +7445,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7027,6 +7512,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7089,6 +7579,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7151,6 +7646,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7213,6 +7713,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7270,6 +7775,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7332,6 +7842,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -7379,6 +7894,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7431,6 +7951,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -7483,6 +8008,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -7535,6 +8065,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -7587,6 +8122,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7639,6 +8179,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7691,6 +8236,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7743,6 +8293,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -7795,6 +8350,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -7847,6 +8407,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7899,6 +8464,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7951,6 +8521,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8003,6 +8578,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8055,6 +8635,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8107,6 +8692,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8159,6 +8749,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G202" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8211,6 +8806,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8263,6 +8863,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G204" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8315,6 +8920,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G205" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8367,6 +8977,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8419,6 +9034,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G207" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8471,6 +9091,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8523,6 +9148,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8575,6 +9205,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G210" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8627,6 +9262,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8679,6 +9319,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8731,6 +9376,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8783,6 +9433,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8835,6 +9490,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8887,6 +9547,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G216" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8939,6 +9604,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G217" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -8991,6 +9661,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9038,6 +9713,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9085,6 +9765,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9137,6 +9822,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9189,6 +9879,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -9241,6 +9936,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -9293,6 +9993,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -9345,6 +10050,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -9397,6 +10107,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -9449,6 +10164,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9501,6 +10221,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9553,6 +10278,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9605,6 +10335,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9657,6 +10392,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9704,6 +10444,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -9756,6 +10501,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G233" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -9803,6 +10553,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9850,6 +10605,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9902,6 +10662,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9954,6 +10719,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10001,6 +10771,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10053,6 +10828,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10100,6 +10880,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10152,6 +10937,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G241" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10199,6 +10989,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10275,6 +11070,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10327,6 +11127,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G246" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10379,6 +11184,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G247" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -10431,6 +11241,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10483,6 +11298,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10535,6 +11355,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G250" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10587,6 +11412,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G251" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10639,6 +11469,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G252" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10691,6 +11526,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G253" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10743,6 +11583,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G254" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10795,6 +11640,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -10847,6 +11697,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10899,6 +11754,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G257" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10951,6 +11811,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G258" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11003,6 +11868,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G259" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11055,6 +11925,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G260" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11107,6 +11982,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G261" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11159,6 +12039,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G262" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11206,6 +12091,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G263" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11258,6 +12148,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G264" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11305,6 +12200,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G265" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11352,6 +12252,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G266" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11399,6 +12304,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G267" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11451,6 +12361,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G268" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11498,6 +12413,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G269" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11545,6 +12465,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G270" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11592,6 +12517,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G271" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11644,6 +12574,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G272" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11696,6 +12631,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G273" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -11748,6 +12688,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G274" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11800,6 +12745,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G275" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11852,6 +12802,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G276" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11904,6 +12859,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G277" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11956,6 +12916,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G278" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12008,6 +12973,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G279" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -12055,6 +13025,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G280" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12102,6 +13077,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G281" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12154,6 +13134,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G282" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12206,6 +13191,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G283" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -12253,6 +13243,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G284" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12305,6 +13300,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G285" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12357,6 +13357,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G286" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12409,6 +13414,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G287" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -12456,6 +13466,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G288" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12508,6 +13523,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G289" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -12555,6 +13575,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G290" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12602,6 +13627,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G291" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12654,6 +13684,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G292" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12701,6 +13736,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G293" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12753,6 +13793,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G294" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -12805,6 +13850,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G295" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -13028,6 +14078,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G299" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13194,6 +14249,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G302" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -13246,6 +14306,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G303" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -13298,6 +14363,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G304" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -13345,6 +14415,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G305" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13397,6 +14472,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G306" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13449,6 +14529,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G307" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13501,6 +14586,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G308" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13553,6 +14643,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G309" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13600,6 +14695,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G310" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13652,6 +14752,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G311" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -13704,6 +14809,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G312" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13756,6 +14866,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G313" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -13808,6 +14923,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G314" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13860,6 +14980,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G315" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13912,6 +15037,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G316" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13964,6 +15094,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G317" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14112,6 +15247,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G326" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14164,6 +15304,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G327" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -14216,6 +15361,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G328" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -14268,6 +15418,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G329" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14320,6 +15475,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G330" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14372,6 +15532,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G331" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14424,6 +15589,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G332" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14476,6 +15646,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G333" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14528,6 +15703,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G334" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14580,6 +15760,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G335" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14632,6 +15817,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G336" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14684,6 +15874,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G337" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14736,6 +15931,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G338" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14788,6 +15988,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G339" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14840,6 +16045,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G340" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14892,6 +16102,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G341" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14944,6 +16159,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G342" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14996,6 +16216,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G343" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -15048,6 +16273,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G344" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -15157,6 +16387,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G346" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15209,6 +16444,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G347" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15318,6 +16558,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G349" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15370,6 +16615,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G350" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15422,6 +16672,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G351" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15474,6 +16729,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G352" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15521,6 +16781,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G353" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15620,6 +16885,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G355" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -15667,6 +16937,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G356" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15714,6 +16989,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G357" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15761,6 +17041,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G358" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -15808,6 +17093,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G359" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15855,6 +17145,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G360" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -15954,6 +17249,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G362" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16001,6 +17301,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G363" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16048,6 +17353,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G364" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16095,6 +17405,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G365" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -16142,6 +17457,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G366" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16189,6 +17509,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G367" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16236,6 +17561,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G368" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -16283,6 +17613,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G369" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16330,6 +17665,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G370" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -16377,6 +17717,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G371" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16424,6 +17769,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G372" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16471,6 +17821,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G373" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -16518,6 +17873,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G374" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16565,6 +17925,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G375" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16612,6 +17977,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G376" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16659,6 +18029,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G377" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16706,6 +18081,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G378" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -16753,6 +18133,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G379" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -16800,6 +18185,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16847,6 +18237,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G381" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16894,6 +18289,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G382" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16941,6 +18341,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G383" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16983,6 +18388,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G384" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17030,6 +18440,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G385" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -17077,6 +18492,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G386" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -17124,6 +18544,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G387" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17171,6 +18596,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G388" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17218,6 +18648,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G389" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -17265,6 +18700,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G390" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17312,6 +18752,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G391" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -17359,6 +18804,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G392" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -17406,6 +18856,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G393" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -17453,6 +18908,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G394" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -17639,6 +19099,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G407" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17681,6 +19146,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G408" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17728,6 +19198,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G409" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17775,6 +19250,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G410" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17822,6 +19302,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G411" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17881,6 +19366,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G413" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17928,6 +19418,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G414" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17987,6 +19482,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G416" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -18034,6 +19534,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G417" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -18081,6 +19586,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G418" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -18128,6 +19638,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G419" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18175,6 +19690,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G420" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18222,6 +19742,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G421" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18269,6 +19794,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G422" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18316,6 +19846,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G423" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18358,6 +19893,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G424" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18457,6 +19997,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G426" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -18504,6 +20049,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G427" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18551,6 +20101,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G428" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18598,6 +20153,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G429" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18645,6 +20205,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G430" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18744,6 +20309,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G432" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18791,6 +20361,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G433" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18890,6 +20465,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G435" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -18944,6 +20524,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G437" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18991,6 +20576,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G438" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19038,6 +20628,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G439" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19132,6 +20727,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G441" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19179,6 +20779,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G442" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19226,6 +20831,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G443" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -19273,6 +20883,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G444" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -19315,6 +20930,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G445" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19357,6 +20977,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G446" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19404,6 +21029,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G447" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19451,6 +21081,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G448" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -19498,6 +21133,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G449" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19545,6 +21185,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G450" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19592,6 +21237,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G451" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -19639,6 +21289,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G452" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -19686,6 +21341,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G453" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19733,6 +21393,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G454" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19780,6 +21445,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G455" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19827,6 +21497,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G456" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19869,6 +21544,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G457" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19911,6 +21591,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G458" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19958,6 +21643,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G459" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20005,6 +21695,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G460" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20047,6 +21742,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G461" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20094,6 +21794,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G462" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -20136,6 +21841,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G463" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20183,6 +21893,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G464" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20230,6 +21945,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G465" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20277,6 +21997,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G466" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20319,6 +22044,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G467" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20366,6 +22096,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G468" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -20413,6 +22148,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G469" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20455,6 +22195,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G470" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20502,6 +22247,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G471" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20549,6 +22299,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G472" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20596,6 +22351,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G473" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20643,6 +22403,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G474" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -20737,6 +22502,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G476" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20784,6 +22554,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G477" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -20831,6 +22606,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G478" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20925,6 +22705,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G480" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21024,6 +22809,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G482" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -21251,6 +23041,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G488" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21298,6 +23093,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G489" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21345,6 +23145,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G490" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21392,6 +23197,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G491" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21439,6 +23249,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G492" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21486,6 +23301,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G493" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21533,6 +23353,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G494" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21580,6 +23405,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G495" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -21627,6 +23457,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G496" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21674,6 +23509,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G497" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21721,6 +23561,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G498" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -21768,6 +23613,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G499" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21815,6 +23665,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G500" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21862,6 +23717,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G501" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21909,6 +23769,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G502" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21956,6 +23821,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G503" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22003,6 +23873,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G504" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22050,6 +23925,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G505" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22097,6 +23977,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G506" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -22144,6 +24029,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G507" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22191,6 +24081,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G508" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22238,6 +24133,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G509" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22285,6 +24185,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G510" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22332,6 +24237,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G511" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22379,6 +24289,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G512" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22426,6 +24341,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G513" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -22473,6 +24393,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G514" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22520,6 +24445,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G515" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22567,6 +24497,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G516" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22614,6 +24549,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G517" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22661,6 +24601,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G518" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22708,6 +24653,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G519" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22755,6 +24705,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G520" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22802,6 +24757,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G521" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22849,6 +24809,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G522" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22896,6 +24861,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G523" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22943,6 +24913,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G524" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22990,6 +24965,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G525" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23037,6 +25017,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G526" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23084,6 +25069,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G527" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -23131,6 +25121,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G528" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23178,6 +25173,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G529" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23225,6 +25225,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G530" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23267,6 +25272,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G531" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23314,6 +25324,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G532" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -23361,6 +25376,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G533" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -23408,6 +25428,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G534" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23455,6 +25480,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G535" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -23502,6 +25532,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G536" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23549,6 +25584,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G537" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -23596,6 +25636,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G538" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23643,6 +25688,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G539" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23685,6 +25735,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G540" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23727,6 +25782,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G541" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23774,6 +25834,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G542" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -23821,6 +25886,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G543" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23868,6 +25938,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G544" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23915,6 +25990,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G545" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23962,6 +26042,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G546" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -24009,6 +26094,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G547" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -24056,6 +26146,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G548" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24098,6 +26193,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G549" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24140,6 +26240,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G550" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24403,6 +26508,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G569" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24450,6 +26560,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G570" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24497,6 +26612,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G571" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24544,6 +26664,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G572" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24591,6 +26716,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G573" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24638,6 +26768,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G574" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24685,6 +26820,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G575" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24732,6 +26872,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G576" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24779,6 +26924,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G577" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24826,6 +26976,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G578" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24873,6 +27028,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G579" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24920,6 +27080,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G580" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24967,6 +27132,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G581" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25014,6 +27184,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G582" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25061,6 +27236,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G583" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25108,6 +27288,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G584" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25155,6 +27340,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G585" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25202,6 +27392,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G586" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25249,6 +27444,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G587" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25296,6 +27496,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G588" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25343,6 +27548,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G589" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25390,6 +27600,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G590" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25437,6 +27652,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G591" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25484,6 +27704,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G592" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25531,6 +27756,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G593" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25578,6 +27808,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G594" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25625,6 +27860,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G595" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25672,6 +27912,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G596" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25719,6 +27964,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G597" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25766,6 +28016,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G598" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25813,6 +28068,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G599" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25860,6 +28120,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G600" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25907,6 +28172,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G601" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25954,6 +28224,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G602" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -26001,6 +28276,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G603" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -26048,6 +28328,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G604" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -26095,6 +28380,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G605" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -26142,6 +28432,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G606" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -26189,6 +28484,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G607" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26236,6 +28536,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G608" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26283,6 +28588,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G609" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26330,6 +28640,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G610" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26377,6 +28692,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G611" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26424,6 +28744,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G612" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26471,6 +28796,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G613" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26518,6 +28848,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G614" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26565,6 +28900,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G615" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26612,6 +28952,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G616" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26659,6 +29004,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G617" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26706,6 +29056,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G618" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26753,6 +29108,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G619" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26800,6 +29160,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G620" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26847,6 +29212,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G621" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26894,6 +29264,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G622" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26941,6 +29316,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G623" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26988,6 +29368,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G624" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27035,6 +29420,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G625" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27082,6 +29472,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G626" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27129,6 +29524,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G627" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27176,6 +29576,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G628" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27223,6 +29628,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G629" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27330,6 +29740,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G635" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27449,6 +29864,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G637" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27511,6 +29931,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G638" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27573,6 +29998,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G639" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27635,6 +30065,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G640" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27697,6 +30132,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G641" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27759,6 +30199,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G642" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27821,6 +30266,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G643" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27883,6 +30333,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G644" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27945,6 +30400,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G645" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28007,6 +30467,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G646" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28069,6 +30534,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G647" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28129,6 +30599,11 @@
       <c r="E648" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -28289,6 +30764,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28346,6 +30826,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28403,6 +30888,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28460,6 +30950,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28517,6 +31012,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28574,6 +31074,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28626,6 +31131,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28678,6 +31188,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28740,6 +31255,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28802,6 +31322,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28859,6 +31384,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28916,6 +31446,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28978,6 +31513,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29030,6 +31570,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29082,6 +31627,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30141,6 +32691,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30260,6 +32815,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30317,6 +32877,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31490,6 +34055,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31552,6 +34122,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31872,6 +34447,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31924,6 +34504,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31976,6 +34561,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32028,6 +34618,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32080,6 +34675,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32132,6 +34732,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32251,6 +34856,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32303,6 +34913,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32355,6 +34970,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32407,6 +35027,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32464,6 +35089,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32526,6 +35156,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32588,6 +35223,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32712,6 +35352,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32769,6 +35414,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32826,6 +35476,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32888,6 +35543,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32950,6 +35610,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33012,6 +35677,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33074,6 +35744,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33312,6 +35987,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33364,6 +36044,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33545,6 +36230,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33607,6 +36297,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33664,6 +36359,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33721,6 +36421,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33969,6 +36674,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34031,6 +36741,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34294,6 +37009,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34490,6 +37210,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35303,6 +38028,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35365,6 +38095,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35427,6 +38162,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35489,6 +38229,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35551,6 +38296,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35613,6 +38363,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35675,6 +38430,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35737,6 +38497,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35856,6 +38621,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35918,6 +38688,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35975,6 +38750,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36032,6 +38812,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38066,6 +40851,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38195,6 +40985,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G210" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38252,6 +41047,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38562,6 +41362,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G216" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38624,6 +41429,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G217" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38810,6 +41620,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38872,6 +41687,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38934,6 +41754,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38991,6 +41816,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39053,6 +41883,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39115,6 +41950,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39177,6 +42017,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39239,6 +42084,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39301,6 +42151,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39358,6 +42213,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39420,6 +42280,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39482,6 +42347,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39544,6 +42414,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39604,6 +42479,11 @@
       <c r="E233" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -40847,6 +43727,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -41043,6 +43928,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -41105,6 +43995,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41368,6 +44263,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41430,6 +44330,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41492,6 +44397,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41554,6 +44464,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41683,6 +44598,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41745,6 +44665,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41817,6 +44742,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41879,6 +44809,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">EnzaR</t>
@@ -41941,6 +44876,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42013,6 +44953,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42085,6 +45030,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42157,6 +45107,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42219,6 +45174,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42616,6 +45576,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -42745,6 +45710,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -42807,6 +45777,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -42869,6 +45844,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -42931,6 +45911,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -42993,6 +45978,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -43055,6 +46045,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -43117,6 +46112,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -43179,6 +46179,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -43241,6 +46246,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -43303,6 +46313,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -43365,6 +46380,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -43427,6 +46447,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43489,6 +46514,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43551,6 +46581,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43613,6 +46648,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43675,6 +46715,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43747,6 +46792,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43809,6 +46859,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43871,6 +46926,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43943,6 +47003,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -45087,6 +48152,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -45149,6 +48219,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -45211,6 +48286,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45273,6 +48353,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45335,6 +48420,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45397,6 +48487,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45459,6 +48554,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45521,6 +48621,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45583,6 +48688,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45645,6 +48755,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -45707,6 +48822,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -46372,6 +49492,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -46429,6 +49554,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -46491,6 +49621,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -46620,6 +49755,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -46950,6 +50090,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -47012,6 +50157,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -47074,6 +50224,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -47136,6 +50291,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -47198,6 +50358,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -47260,6 +50425,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -47322,6 +50492,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -47384,6 +50559,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -47446,6 +50626,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -48245,6 +51430,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -48307,6 +51497,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -48637,6 +51832,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -48699,6 +51899,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -48771,6 +51976,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -48843,6 +52053,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -48905,6 +52120,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -48967,6 +52187,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49029,6 +52254,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49091,6 +52321,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49153,6 +52388,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49210,6 +52450,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49473,6 +52718,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49535,6 +52785,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49597,6 +52852,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -49860,6 +53120,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -49922,6 +53187,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -49984,6 +53254,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G157" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50046,6 +53321,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50108,6 +53388,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50170,6 +53455,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50232,6 +53522,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -50294,6 +53589,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -50356,6 +53656,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50418,6 +53723,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50480,6 +53790,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50542,6 +53857,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50604,6 +53924,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50666,6 +53991,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -50728,6 +54058,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -50790,6 +54125,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50852,6 +54192,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50914,6 +54259,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -50976,6 +54326,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51038,6 +54393,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51100,6 +54460,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51162,6 +54527,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51224,6 +54594,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51286,6 +54661,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51348,6 +54728,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51410,6 +54795,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51472,6 +54862,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51534,6 +54929,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51596,6 +54996,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51658,6 +55063,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51720,6 +55130,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51782,6 +55197,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51844,6 +55264,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51906,6 +55331,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -51968,6 +55398,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52030,6 +55465,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52092,6 +55532,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52154,6 +55599,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52216,6 +55666,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52278,6 +55733,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52350,6 +55810,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52422,6 +55887,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52494,6 +55964,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52566,6 +56041,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -52628,6 +56108,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53037,6 +56522,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53379,6 +56869,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53508,6 +57003,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53570,6 +57070,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53632,6 +57137,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G216" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53694,6 +57204,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G217" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53756,6 +57271,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53818,6 +57338,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53880,6 +57405,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -53942,6 +57472,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54004,6 +57539,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54066,6 +57606,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54138,6 +57683,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54210,6 +57760,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54282,6 +57837,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54354,6 +57914,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -54416,6 +57981,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -54478,6 +58048,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -54540,6 +58115,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -54602,6 +58182,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -54664,6 +58249,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -54726,6 +58316,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G233" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -54822,6 +58417,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54884,6 +58484,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -54946,6 +58551,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55008,6 +58618,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55350,6 +58965,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55412,6 +59032,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G246" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55474,6 +59099,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G247" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55536,6 +59166,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55598,6 +59233,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55660,6 +59300,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G250" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55722,6 +59367,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G251" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55784,6 +59434,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G252" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55846,6 +59501,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G253" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -55975,6 +59635,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -56047,6 +59712,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -56645,6 +60315,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G265" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -56908,6 +60583,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G269" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -56970,6 +60650,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G270" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57032,6 +60717,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G271" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57439,6 +61129,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G277" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57568,6 +61263,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G279" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57630,6 +61330,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G280" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57692,6 +61397,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G281" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57754,6 +61464,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G282" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57816,6 +61531,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G283" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -57878,6 +61598,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G284" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58000,6 +61725,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G290" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -58062,6 +61792,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G291" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58258,6 +61993,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G294" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58320,6 +62060,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G295" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58382,6 +62127,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G296" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58444,6 +62194,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G297" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -58506,6 +62261,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G298" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -58568,6 +62328,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G299" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58630,6 +62395,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G300" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58692,6 +62462,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G301" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58754,6 +62529,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G302" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58816,6 +62596,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G303" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58878,6 +62663,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G304" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -58940,6 +62730,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G305" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59002,6 +62797,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G306" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59064,6 +62864,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G307" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59126,6 +62931,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G308" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59188,6 +62998,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G309" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59250,6 +63065,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G310" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59312,6 +63132,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G311" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59374,6 +63199,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G312" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59436,6 +63266,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G313" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59498,6 +63333,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G314" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59560,6 +63400,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G315" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59622,6 +63467,11 @@
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G316" t="inlineStr">
         <is>
           <t xml:space="preserve">CR</t>
@@ -59684,6 +63534,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G317" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59746,6 +63601,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G318" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59808,6 +63668,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G319" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59870,6 +63735,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G320" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59932,6 +63802,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G321" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -59994,6 +63869,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G322" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60056,6 +63936,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G323" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60118,6 +64003,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G324" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60180,6 +64070,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G325" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60376,6 +64271,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G328" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60675,6 +64575,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G335" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60732,6 +64637,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G336" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60789,6 +64699,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G337" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60851,6 +64766,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G338" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60913,6 +64833,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G339" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -60975,6 +64900,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G340" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61037,6 +64967,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G341" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61106,6 +65041,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G343" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61168,6 +65108,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G344" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61230,6 +65175,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G345" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61292,6 +65242,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G346" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61354,6 +65309,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G347" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61416,6 +65376,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G348" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61478,6 +65443,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G349" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -61540,6 +65510,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G350" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61602,6 +65577,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G351" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61664,6 +65644,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G352" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -61726,6 +65711,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G353" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -61788,6 +65778,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G354" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -62044,6 +66039,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G362" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -62106,6 +66106,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G363" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -62168,6 +66173,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G364" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -62230,6 +66240,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G365" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -62292,6 +66307,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G366" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -62354,6 +66374,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G367" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -62447,6 +66472,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G371" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -62504,6 +66534,11 @@
           <t xml:space="preserve">cell</t>
         </is>
       </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G372" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -62650,6 +66685,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -62801,6 +66841,11 @@
       <c r="D389" t="inlineStr">
         <is>
           <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
